--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/121.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/121.xlsx
@@ -426,13 +426,13 @@
         <v>-17.26117994135911</v>
       </c>
       <c r="E2">
-        <v>-5.621554611875423</v>
+        <v>-3.970237508030412</v>
       </c>
       <c r="F2">
-        <v>-2.889722313283241</v>
+        <v>-3.352513647745914</v>
       </c>
       <c r="G2">
-        <v>-5.941695452550396</v>
+        <v>-5.574214966054677</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-17.44072807596161</v>
       </c>
       <c r="E3">
-        <v>-5.546631009418516</v>
+        <v>-6.325043992018998</v>
       </c>
       <c r="F3">
-        <v>-2.742145469405973</v>
+        <v>-3.249466654946015</v>
       </c>
       <c r="G3">
-        <v>-5.064586275193731</v>
+        <v>-5.372225340521585</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-17.56923777307852</v>
       </c>
       <c r="E4">
-        <v>-7.464779387217488</v>
+        <v>-4.166832150125405</v>
       </c>
       <c r="F4">
-        <v>-2.592274627510192</v>
+        <v>-3.202155816281135</v>
       </c>
       <c r="G4">
-        <v>-4.537875169350146</v>
+        <v>-5.249139257371482</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-17.57058976338584</v>
       </c>
       <c r="E5">
-        <v>-6.439913263697564</v>
+        <v>-7.04575968728775</v>
       </c>
       <c r="F5">
-        <v>-2.702950331704763</v>
+        <v>-3.10974420055637</v>
       </c>
       <c r="G5">
-        <v>-5.207300582846172</v>
+        <v>-5.632758653371148</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-17.42037698410962</v>
       </c>
       <c r="E6">
-        <v>-7.938059262707132</v>
+        <v>-6.357218799843495</v>
       </c>
       <c r="F6">
-        <v>-2.298277045073929</v>
+        <v>-2.891796968032466</v>
       </c>
       <c r="G6">
-        <v>-5.355579917550129</v>
+        <v>-5.103544775099874</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-17.08542921180409</v>
       </c>
       <c r="E7">
-        <v>-8.716023926380855</v>
+        <v>-8.187781961860114</v>
       </c>
       <c r="F7">
-        <v>-2.174382147603185</v>
+        <v>-2.527831258252088</v>
       </c>
       <c r="G7">
-        <v>-5.311847610976357</v>
+        <v>-4.707457864599313</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-16.57394982182002</v>
       </c>
       <c r="E8">
-        <v>-9.136528965785107</v>
+        <v>-9.02914526164122</v>
       </c>
       <c r="F8">
-        <v>-2.118765563264783</v>
+        <v>-2.567630579760039</v>
       </c>
       <c r="G8">
-        <v>-4.769315408000595</v>
+        <v>-4.923755667953134</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-15.90736706126983</v>
       </c>
       <c r="E9">
-        <v>-10.39762293591516</v>
+        <v>-9.526539261221711</v>
       </c>
       <c r="F9">
-        <v>-2.094397872196874</v>
+        <v>-2.166252985139235</v>
       </c>
       <c r="G9">
-        <v>-3.942801298120611</v>
+        <v>-4.857346124435355</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-15.11518455149478</v>
       </c>
       <c r="E10">
-        <v>-11.18837148171253</v>
+        <v>-10.79484256197197</v>
       </c>
       <c r="F10">
-        <v>-1.964344734273944</v>
+        <v>-2.174439161016141</v>
       </c>
       <c r="G10">
-        <v>-4.289216783349948</v>
+        <v>-3.115042423117861</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-14.26074524624206</v>
       </c>
       <c r="E11">
-        <v>-11.63481562023272</v>
+        <v>-11.03852880527273</v>
       </c>
       <c r="F11">
-        <v>-2.037665567041044</v>
+        <v>-2.443586813933244</v>
       </c>
       <c r="G11">
-        <v>-3.23323883050646</v>
+        <v>-4.093146413241072</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-13.41282537833316</v>
       </c>
       <c r="E12">
-        <v>-12.19689434253877</v>
+        <v>-11.18473964555838</v>
       </c>
       <c r="F12">
-        <v>-2.091120392804872</v>
+        <v>-2.357124389479828</v>
       </c>
       <c r="G12">
-        <v>-2.539490838933408</v>
+        <v>-2.899413349962972</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-12.63524069159415</v>
       </c>
       <c r="E13">
-        <v>-13.09604549913176</v>
+        <v>-11.56087016816147</v>
       </c>
       <c r="F13">
-        <v>-2.001915781558872</v>
+        <v>-2.149442738699803</v>
       </c>
       <c r="G13">
-        <v>-2.257832934997755</v>
+        <v>-3.355364855450174</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-12.00683039824538</v>
       </c>
       <c r="E14">
-        <v>-14.05394454902626</v>
+        <v>-13.54141638931213</v>
       </c>
       <c r="F14">
-        <v>-1.974280113334453</v>
+        <v>-1.618575013609007</v>
       </c>
       <c r="G14">
-        <v>-1.246573831298742</v>
+        <v>-1.907199814751386</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-11.56890285115419</v>
       </c>
       <c r="E15">
-        <v>-14.10427400914751</v>
+        <v>-14.08621898327892</v>
       </c>
       <c r="F15">
-        <v>-2.192685828720877</v>
+        <v>-1.932889959234443</v>
       </c>
       <c r="G15">
-        <v>-1.202536954535357</v>
+        <v>-1.190354146950839</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-11.32838016866755</v>
       </c>
       <c r="E16">
-        <v>-14.19466235034061</v>
+        <v>-15.37994060863424</v>
       </c>
       <c r="F16">
-        <v>-1.391059029944018</v>
+        <v>-1.85996267738733</v>
       </c>
       <c r="G16">
-        <v>-0.299675043428701</v>
+        <v>-1.222939846693885</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-11.27207697915933</v>
       </c>
       <c r="E17">
-        <v>-15.41993609106998</v>
+        <v>-14.93087901213761</v>
       </c>
       <c r="F17">
-        <v>-1.581660412426029</v>
+        <v>-1.300897860325093</v>
       </c>
       <c r="G17">
-        <v>0.4719833268655592</v>
+        <v>-0.4122302812183821</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-11.3455891713611</v>
       </c>
       <c r="E18">
-        <v>-17.10150340128623</v>
+        <v>-15.72704814132217</v>
       </c>
       <c r="F18">
-        <v>-1.370896869934559</v>
+        <v>-1.340099332849966</v>
       </c>
       <c r="G18">
-        <v>0.4663752627220338</v>
+        <v>-0.08670102779630703</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-11.48893597011588</v>
       </c>
       <c r="E19">
-        <v>-17.78403953219631</v>
+        <v>-16.6715066803619</v>
       </c>
       <c r="F19">
-        <v>-1.077110712238006</v>
+        <v>-0.9124282607680777</v>
       </c>
       <c r="G19">
-        <v>1.334969716951694</v>
+        <v>1.432667226361126</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-11.64933125462045</v>
       </c>
       <c r="E20">
-        <v>-18.79148461620873</v>
+        <v>-18.68529642920287</v>
       </c>
       <c r="F20">
-        <v>-1.16692188284962</v>
+        <v>-0.4615463947895093</v>
       </c>
       <c r="G20">
-        <v>1.633081032217525</v>
+        <v>0.6677458162392823</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-11.77001873699433</v>
       </c>
       <c r="E21">
-        <v>-19.05971066015706</v>
+        <v>-19.17691209594957</v>
       </c>
       <c r="F21">
-        <v>-1.009906943569291</v>
+        <v>-0.4687768041464481</v>
       </c>
       <c r="G21">
-        <v>2.365433295324018</v>
+        <v>1.409493407586227</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-11.82459640779877</v>
       </c>
       <c r="E22">
-        <v>-19.67547444182404</v>
+        <v>-20.04824483671344</v>
       </c>
       <c r="F22">
-        <v>-0.705434730208311</v>
+        <v>0.04771007937919942</v>
       </c>
       <c r="G22">
-        <v>1.592616234091013</v>
+        <v>1.351409886099714</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-11.80134773276555</v>
       </c>
       <c r="E23">
-        <v>-19.94243704152422</v>
+        <v>-18.94169862751717</v>
       </c>
       <c r="F23">
-        <v>-0.09766541327560693</v>
+        <v>-0.3902036107107931</v>
       </c>
       <c r="G23">
-        <v>2.754452191098236</v>
+        <v>0.761593161186542</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-11.69278383353258</v>
       </c>
       <c r="E24">
-        <v>-20.26671653673949</v>
+        <v>-19.814783887722</v>
       </c>
       <c r="F24">
-        <v>-0.3156886636834516</v>
+        <v>0.008243336113490672</v>
       </c>
       <c r="G24">
-        <v>2.136754051653322</v>
+        <v>1.919489569002032</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-11.51730399883274</v>
       </c>
       <c r="E25">
-        <v>-20.54431652188369</v>
+        <v>-20.20123933106258</v>
       </c>
       <c r="F25">
-        <v>-0.1202126343937183</v>
+        <v>0.1369138987722417</v>
       </c>
       <c r="G25">
-        <v>2.113355115781753</v>
+        <v>1.641757972075955</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-11.29305329078071</v>
       </c>
       <c r="E26">
-        <v>-20.93770053045601</v>
+        <v>-20.38032236416992</v>
       </c>
       <c r="F26">
-        <v>-0.4818352512722041</v>
+        <v>-0.09650930795733614</v>
       </c>
       <c r="G26">
-        <v>2.564552677874562</v>
+        <v>1.698249121158078</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-11.03396864574603</v>
       </c>
       <c r="E27">
-        <v>-21.48437338418796</v>
+        <v>-20.84181009334359</v>
       </c>
       <c r="F27">
-        <v>-0.2339900266236769</v>
+        <v>-0.2190548879881251</v>
       </c>
       <c r="G27">
-        <v>2.169518520855489</v>
+        <v>0.6633096852166589</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-10.7682987307214</v>
       </c>
       <c r="E28">
-        <v>-20.90319808699157</v>
+        <v>-21.74191222947819</v>
       </c>
       <c r="F28">
-        <v>-0.3848926529233669</v>
+        <v>0.254065376455044</v>
       </c>
       <c r="G28">
-        <v>1.64768384859125</v>
+        <v>1.136777287152146</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-10.51207220822581</v>
       </c>
       <c r="E29">
-        <v>-21.48062833618362</v>
+        <v>-20.32070047538493</v>
       </c>
       <c r="F29">
-        <v>-0.09835432534882309</v>
+        <v>0.1005021242174157</v>
       </c>
       <c r="G29">
-        <v>1.525604171285086</v>
+        <v>0.5317155000306293</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-10.27846969951266</v>
       </c>
       <c r="E30">
-        <v>-21.01784999191776</v>
+        <v>-19.65774546608401</v>
       </c>
       <c r="F30">
-        <v>-0.05990352942786875</v>
+        <v>-0.3140368584136483</v>
       </c>
       <c r="G30">
-        <v>1.387796092121844</v>
+        <v>0.4743106403796669</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-10.08746530856233</v>
       </c>
       <c r="E31">
-        <v>-21.48803691966017</v>
+        <v>-20.63691022991852</v>
       </c>
       <c r="F31">
-        <v>-0.2515010629306908</v>
+        <v>-0.1401799985755789</v>
       </c>
       <c r="G31">
-        <v>1.494193715208481</v>
+        <v>0.2357725920930208</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.942457346048402</v>
       </c>
       <c r="E32">
-        <v>-20.08127552612539</v>
+        <v>-19.25175418587434</v>
       </c>
       <c r="F32">
-        <v>-0.2424976948014176</v>
+        <v>0.1210681292353123</v>
       </c>
       <c r="G32">
-        <v>0.6718144767070466</v>
+        <v>0.5614773044286773</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.845647921702247</v>
       </c>
       <c r="E33">
-        <v>-20.90476493899822</v>
+        <v>-18.71417903642379</v>
       </c>
       <c r="F33">
-        <v>0.01491232172340618</v>
+        <v>0.1856754120556646</v>
       </c>
       <c r="G33">
-        <v>0.4318032356554248</v>
+        <v>0.8825009053718043</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.797233447514971</v>
       </c>
       <c r="E34">
-        <v>-19.81837949608409</v>
+        <v>-18.70917960111932</v>
       </c>
       <c r="F34">
-        <v>0.1996341959943479</v>
+        <v>0.1294586031753105</v>
       </c>
       <c r="G34">
-        <v>0.4429134264852189</v>
+        <v>0.2896285469258844</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-9.779360087316538</v>
       </c>
       <c r="E35">
-        <v>-19.40469433853539</v>
+        <v>-19.0228352963126</v>
       </c>
       <c r="F35">
-        <v>-0.05343250705738317</v>
+        <v>-0.09977253399609912</v>
       </c>
       <c r="G35">
-        <v>-0.1780853268623489</v>
+        <v>-0.2935108076345781</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-9.78107843525458</v>
       </c>
       <c r="E36">
-        <v>-18.02554305102538</v>
+        <v>-18.00757406616294</v>
       </c>
       <c r="F36">
-        <v>0.08868767808823741</v>
+        <v>0.2346428071080946</v>
       </c>
       <c r="G36">
-        <v>-0.4046921690254616</v>
+        <v>-0.3340914748549643</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-9.789114102823492</v>
       </c>
       <c r="E37">
-        <v>-18.07100440158838</v>
+        <v>-17.0393183962129</v>
       </c>
       <c r="F37">
-        <v>-0.05942762580027919</v>
+        <v>0.5237016026470602</v>
       </c>
       <c r="G37">
-        <v>0.1405546812925029</v>
+        <v>-0.2540888313529368</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-9.783341053710522</v>
       </c>
       <c r="E38">
-        <v>-17.37915772811852</v>
+        <v>-17.97148212832181</v>
       </c>
       <c r="F38">
-        <v>0.2272017648644024</v>
+        <v>0.2900360889124202</v>
       </c>
       <c r="G38">
-        <v>-0.3417289034140629</v>
+        <v>-0.620149093812309</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-9.763464260986018</v>
       </c>
       <c r="E39">
-        <v>-17.22348690563085</v>
+        <v>-17.28376089467294</v>
       </c>
       <c r="F39">
-        <v>0.3924020881686797</v>
+        <v>0.5957950633296948</v>
       </c>
       <c r="G39">
-        <v>-0.42818380017213</v>
+        <v>-0.6111675837642663</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-9.729270424552205</v>
       </c>
       <c r="E40">
-        <v>-17.48735655758379</v>
+        <v>-16.19608483666663</v>
       </c>
       <c r="F40">
-        <v>0.386570091135074</v>
+        <v>0.5247207174036456</v>
       </c>
       <c r="G40">
-        <v>-0.4483052959598203</v>
+        <v>-0.1846269648479487</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-9.680355982308139</v>
       </c>
       <c r="E41">
-        <v>-16.4332817767144</v>
+        <v>-15.25485509959437</v>
       </c>
       <c r="F41">
-        <v>0.6926054222345928</v>
+        <v>0.5865097955474733</v>
       </c>
       <c r="G41">
-        <v>-0.4309712795161963</v>
+        <v>-0.3580366507405128</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-9.634673713200112</v>
       </c>
       <c r="E42">
-        <v>-16.14129482964782</v>
+        <v>-14.80024612243835</v>
       </c>
       <c r="F42">
-        <v>0.3724584795755507</v>
+        <v>0.2340900937436062</v>
       </c>
       <c r="G42">
-        <v>-1.075034603635866</v>
+        <v>-0.03441758209459717</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-9.602245571213302</v>
       </c>
       <c r="E43">
-        <v>-14.14468611119196</v>
+        <v>-14.80871436883269</v>
       </c>
       <c r="F43">
-        <v>0.3878774403682692</v>
+        <v>0.4950531544897184</v>
       </c>
       <c r="G43">
-        <v>-0.6420814580099806</v>
+        <v>-0.186461007076705</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-9.593745783606167</v>
       </c>
       <c r="E44">
-        <v>-13.11917694436294</v>
+        <v>-13.57159866857326</v>
       </c>
       <c r="F44">
-        <v>0.815591272509874</v>
+        <v>0.1871268785271649</v>
       </c>
       <c r="G44">
-        <v>-0.5819189139248053</v>
+        <v>-1.152296115431378</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-9.627719460109226</v>
       </c>
       <c r="E45">
-        <v>-13.96913528781061</v>
+        <v>-12.66854849585966</v>
       </c>
       <c r="F45">
-        <v>0.8066987637946814</v>
+        <v>0.3134052534006446</v>
       </c>
       <c r="G45">
-        <v>-0.09892025138175699</v>
+        <v>-0.1150657819767826</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-9.708850359280998</v>
       </c>
       <c r="E46">
-        <v>-13.51617467519338</v>
+        <v>-12.87612015894925</v>
       </c>
       <c r="F46">
-        <v>0.6800355483837499</v>
+        <v>0.1803866261510546</v>
       </c>
       <c r="G46">
-        <v>0.1803176437646891</v>
+        <v>-0.1601818965859703</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-9.845127166305391</v>
       </c>
       <c r="E47">
-        <v>-13.43268319991396</v>
+        <v>-13.11433600564874</v>
       </c>
       <c r="F47">
-        <v>0.7083522101518072</v>
+        <v>0.4305385184654194</v>
       </c>
       <c r="G47">
-        <v>-0.4831587193972673</v>
+        <v>-0.5985941318061143</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-10.04484432150214</v>
       </c>
       <c r="E48">
-        <v>-12.20338364579177</v>
+        <v>-12.33300668578732</v>
       </c>
       <c r="F48">
-        <v>0.5199798937457776</v>
+        <v>0.3051343492572621</v>
       </c>
       <c r="G48">
-        <v>0.09037343200823023</v>
+        <v>-0.4576145500162508</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-10.29974434990171</v>
       </c>
       <c r="E49">
-        <v>-11.05432412261148</v>
+        <v>-11.29292036112762</v>
       </c>
       <c r="F49">
-        <v>0.5735344929822779</v>
+        <v>0.249369688415766</v>
       </c>
       <c r="G49">
-        <v>0.7258591326356487</v>
+        <v>-0.245143737305826</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-10.61259800813419</v>
       </c>
       <c r="E50">
-        <v>-11.85888451413225</v>
+        <v>-9.08567420267897</v>
       </c>
       <c r="F50">
-        <v>0.5847946420410524</v>
+        <v>0.08871776850063075</v>
       </c>
       <c r="G50">
-        <v>-0.3636314727018811</v>
+        <v>-0.4315804198954222</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-10.97936023160025</v>
       </c>
       <c r="E51">
-        <v>-9.703598066447613</v>
+        <v>-10.12464199425878</v>
       </c>
       <c r="F51">
-        <v>0.8032146107807147</v>
+        <v>0.2578084653861851</v>
       </c>
       <c r="G51">
-        <v>0.06380961460111821</v>
+        <v>0.2803325350516109</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-11.38227306306639</v>
       </c>
       <c r="E52">
-        <v>-10.94528299698079</v>
+        <v>-9.136039890592279</v>
       </c>
       <c r="F52">
-        <v>0.4411477643929482</v>
+        <v>0.6047208298691115</v>
       </c>
       <c r="G52">
-        <v>-0.4617659741224969</v>
+        <v>0.3978701438778952</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-11.81866475017594</v>
       </c>
       <c r="E53">
-        <v>-9.589933368855087</v>
+        <v>-10.28010903541611</v>
       </c>
       <c r="F53">
-        <v>0.6841436815283998</v>
+        <v>0.3746044010909712</v>
       </c>
       <c r="G53">
-        <v>-0.05135433307350857</v>
+        <v>0.7524825398624676</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-12.27498278460397</v>
       </c>
       <c r="E54">
-        <v>-8.746423572394345</v>
+        <v>-9.287943022705575</v>
       </c>
       <c r="F54">
-        <v>0.6670808339954551</v>
+        <v>0.407225575537193</v>
       </c>
       <c r="G54">
-        <v>-0.2547178350053983</v>
+        <v>-1.113440242436952</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-12.73377242263198</v>
       </c>
       <c r="E55">
-        <v>-8.950336228485734</v>
+        <v>-7.755674972048209</v>
       </c>
       <c r="F55">
-        <v>0.582933787590411</v>
+        <v>0.08901788077160652</v>
       </c>
       <c r="G55">
-        <v>-0.129549418711094</v>
+        <v>0.8109269108127611</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-13.19551940251815</v>
       </c>
       <c r="E56">
-        <v>-8.153641796316288</v>
+        <v>-9.189448713038743</v>
       </c>
       <c r="F56">
-        <v>0.6325291220383128</v>
+        <v>0.6022486649351105</v>
       </c>
       <c r="G56">
-        <v>-1.163088493889401</v>
+        <v>0.2042330247403842</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-13.64886823275273</v>
       </c>
       <c r="E57">
-        <v>-7.884546285358492</v>
+        <v>-8.16114094927299</v>
       </c>
       <c r="F57">
-        <v>1.153200948445509</v>
+        <v>-0.07595201332197439</v>
       </c>
       <c r="G57">
-        <v>-0.4393767546404059</v>
+        <v>0.148576133134157</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-14.08677253768488</v>
       </c>
       <c r="E58">
-        <v>-8.323599954298164</v>
+        <v>-7.626147030006813</v>
       </c>
       <c r="F58">
-        <v>0.7152033219419982</v>
+        <v>0.2740889621969027</v>
       </c>
       <c r="G58">
-        <v>-1.216404829799364</v>
+        <v>-1.370567003926605</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-14.51658164106614</v>
       </c>
       <c r="E59">
-        <v>-6.981740650241314</v>
+        <v>-6.88156174824363</v>
       </c>
       <c r="F59">
-        <v>0.9709148138725132</v>
+        <v>0.2236217976425515</v>
       </c>
       <c r="G59">
-        <v>-0.6898824250515173</v>
+        <v>-1.012399082032856</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-14.93288747010932</v>
       </c>
       <c r="E60">
-        <v>-7.506622487048363</v>
+        <v>-6.617343403792096</v>
       </c>
       <c r="F60">
-        <v>0.6889518126876739</v>
+        <v>0.5863941850156462</v>
       </c>
       <c r="G60">
-        <v>-1.501462664003849</v>
+        <v>-0.438621950257452</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-15.34183061805084</v>
       </c>
       <c r="E61">
-        <v>-7.728535827320241</v>
+        <v>-6.347604849525211</v>
       </c>
       <c r="F61">
-        <v>0.6377917767953181</v>
+        <v>0.08173996023720455</v>
       </c>
       <c r="G61">
-        <v>-1.319134368428488</v>
+        <v>-0.3653496458367628</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-15.7536117935894</v>
       </c>
       <c r="E62">
-        <v>-6.096328883787598</v>
+        <v>-6.541382780787433</v>
       </c>
       <c r="F62">
-        <v>1.007870591409293</v>
+        <v>0.3048667029575529</v>
       </c>
       <c r="G62">
-        <v>-2.17904526170864</v>
+        <v>-1.356497185384703</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-16.16142501320293</v>
       </c>
       <c r="E63">
-        <v>-6.718708765979789</v>
+        <v>-6.152065341874005</v>
       </c>
       <c r="F63">
-        <v>0.6720948469237364</v>
+        <v>0.4736675816605818</v>
       </c>
       <c r="G63">
-        <v>-1.883056006133482</v>
+        <v>-2.617527018385108</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-16.57247128705529</v>
       </c>
       <c r="E64">
-        <v>-5.714238889390412</v>
+        <v>-5.708745850419108</v>
       </c>
       <c r="F64">
-        <v>0.7203313616961912</v>
+        <v>0.1225995728555423</v>
       </c>
       <c r="G64">
-        <v>-1.593058837984404</v>
+        <v>-1.68260909482169</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-16.98517664908957</v>
       </c>
       <c r="E65">
-        <v>-5.793079621863953</v>
+        <v>-4.936813114123603</v>
       </c>
       <c r="F65">
-        <v>0.7530047984376225</v>
+        <v>0.3580269594211088</v>
       </c>
       <c r="G65">
-        <v>-2.126086464716919</v>
+        <v>-2.228263142240984</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-17.37823251631068</v>
       </c>
       <c r="E66">
-        <v>-5.599650383100321</v>
+        <v>-5.560479082933973</v>
       </c>
       <c r="F66">
-        <v>0.7053637570893729</v>
+        <v>0.285377617962155</v>
       </c>
       <c r="G66">
-        <v>-2.693553696694471</v>
+        <v>-2.174393945225964</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-17.7459327549918</v>
       </c>
       <c r="E67">
-        <v>-5.185679931689135</v>
+        <v>-3.980729982306184</v>
       </c>
       <c r="F67">
-        <v>0.5858525575925659</v>
+        <v>0.1366557547080251</v>
       </c>
       <c r="G67">
-        <v>-3.090987999229517</v>
+        <v>-3.140629629590888</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-18.06877044823274</v>
       </c>
       <c r="E68">
-        <v>-5.621454985447254</v>
+        <v>-4.75436995330258</v>
       </c>
       <c r="F68">
-        <v>0.1939059316982034</v>
+        <v>-0.5474117621128053</v>
       </c>
       <c r="G68">
-        <v>-2.948833173773212</v>
+        <v>-2.112768140012431</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-18.3190733973886</v>
       </c>
       <c r="E69">
-        <v>-6.350258535293706</v>
+        <v>-5.52903335942471</v>
       </c>
       <c r="F69">
-        <v>0.07814573966211472</v>
+        <v>0.1811380946079306</v>
       </c>
       <c r="G69">
-        <v>-3.20212301298285</v>
+        <v>-2.355785356413711</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-18.49232809753089</v>
       </c>
       <c r="E70">
-        <v>-5.743184895247441</v>
+        <v>-4.402738475080985</v>
       </c>
       <c r="F70">
-        <v>0.2814318146738377</v>
+        <v>-0.2157085173888016</v>
       </c>
       <c r="G70">
-        <v>-3.036860579662433</v>
+        <v>-2.287326585207122</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-18.57655425303474</v>
       </c>
       <c r="E71">
-        <v>-5.490957949968217</v>
+        <v>-5.096917312664789</v>
       </c>
       <c r="F71">
-        <v>-0.2652602999240287</v>
+        <v>-0.363228347853113</v>
       </c>
       <c r="G71">
-        <v>-2.598147084798215</v>
+        <v>-2.070492473475937</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-18.56382329495447</v>
       </c>
       <c r="E72">
-        <v>-6.165560194416862</v>
+        <v>-5.121529568896477</v>
       </c>
       <c r="F72">
-        <v>-0.3303664501077444</v>
+        <v>-0.5346130427571814</v>
       </c>
       <c r="G72">
-        <v>-3.386672684615062</v>
+        <v>-1.978793672583665</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-18.46961227460289</v>
       </c>
       <c r="E73">
-        <v>-5.559251866477894</v>
+        <v>-4.427577155013056</v>
       </c>
       <c r="F73">
-        <v>-0.04869564266430378</v>
+        <v>-0.01306621883170481</v>
       </c>
       <c r="G73">
-        <v>-2.510401075279832</v>
+        <v>-1.700250992000466</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-18.29834815719791</v>
       </c>
       <c r="E74">
-        <v>-5.773444158566694</v>
+        <v>-5.274424436817451</v>
       </c>
       <c r="F74">
-        <v>-0.05241576785967104</v>
+        <v>-0.2904847758921905</v>
       </c>
       <c r="G74">
-        <v>-2.363618107159626</v>
+        <v>-0.9447778788477024</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-18.06364422335613</v>
       </c>
       <c r="E75">
-        <v>-7.075982722814942</v>
+        <v>-6.77628378451331</v>
       </c>
       <c r="F75">
-        <v>0.2133752203696583</v>
+        <v>-0.5883616459683231</v>
       </c>
       <c r="G75">
-        <v>-2.431341937256497</v>
+        <v>-1.432795328428286</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-17.79091633657121</v>
       </c>
       <c r="E76">
-        <v>-7.097483917403361</v>
+        <v>-6.032260033527078</v>
       </c>
       <c r="F76">
-        <v>-0.1730236837029199</v>
+        <v>-0.8907790009040204</v>
       </c>
       <c r="G76">
-        <v>-2.326513512755475</v>
+        <v>-2.780233710549209</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-17.48870299602108</v>
       </c>
       <c r="E77">
-        <v>-7.084844946447953</v>
+        <v>-7.087018613971635</v>
       </c>
       <c r="F77">
-        <v>-0.6437050410363122</v>
+        <v>-0.4391551687040687</v>
       </c>
       <c r="G77">
-        <v>-2.329082496093949</v>
+        <v>-2.372785007757868</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-17.17759787174567</v>
       </c>
       <c r="E78">
-        <v>-7.09632009958339</v>
+        <v>-7.335464283454454</v>
       </c>
       <c r="F78">
-        <v>-0.3136623119646468</v>
+        <v>-0.781722636007987</v>
       </c>
       <c r="G78">
-        <v>-2.170947667319582</v>
+        <v>-1.372722169072671</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-16.87758096379674</v>
       </c>
       <c r="E79">
-        <v>-7.758559609991095</v>
+        <v>-8.321901776545287</v>
       </c>
       <c r="F79">
-        <v>-0.7380464024190402</v>
+        <v>-0.9219170347604332</v>
       </c>
       <c r="G79">
-        <v>-2.898062647382949</v>
+        <v>-1.792539069998729</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-16.58846398600449</v>
       </c>
       <c r="E80">
-        <v>-8.839497298673994</v>
+        <v>-8.743701959515736</v>
       </c>
       <c r="F80">
-        <v>-0.418673891952648</v>
+        <v>-0.5433574749692802</v>
       </c>
       <c r="G80">
-        <v>-1.354202977325988</v>
+        <v>-0.5834550070550272</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-16.32759552388008</v>
       </c>
       <c r="E81">
-        <v>-10.23349292398115</v>
+        <v>-10.18819912695643</v>
       </c>
       <c r="F81">
-        <v>-0.3081621013203257</v>
+        <v>-1.32345695923757</v>
       </c>
       <c r="G81">
-        <v>-1.995660902106252</v>
+        <v>-0.1968925360709485</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-16.10124629204301</v>
       </c>
       <c r="E82">
-        <v>-10.38803615644092</v>
+        <v>-9.622253087847831</v>
       </c>
       <c r="F82">
-        <v>-0.7130935320153762</v>
+        <v>-0.8063104621981421</v>
       </c>
       <c r="G82">
-        <v>-1.583981322115722</v>
+        <v>-1.14874390006774</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-15.89821836105072</v>
       </c>
       <c r="E83">
-        <v>-11.1890598097617</v>
+        <v>-11.30185051187074</v>
       </c>
       <c r="F83">
-        <v>-0.7685311575853341</v>
+        <v>-0.9954809663855532</v>
       </c>
       <c r="G83">
-        <v>-1.982802743231722</v>
+        <v>-0.3676570960776349</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-15.72478755432504</v>
       </c>
       <c r="E84">
-        <v>-12.47192215444662</v>
+        <v>-11.23790845888244</v>
       </c>
       <c r="F84">
-        <v>-0.6812523327325084</v>
+        <v>-1.487506720194281</v>
       </c>
       <c r="G84">
-        <v>-0.8271078481998473</v>
+        <v>-0.3341378224925141</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-15.57198677362969</v>
       </c>
       <c r="E85">
-        <v>-13.47010198063934</v>
+        <v>-13.03233439831785</v>
       </c>
       <c r="F85">
-        <v>-1.121565337284392</v>
+        <v>-1.63711783431993</v>
       </c>
       <c r="G85">
-        <v>-1.16168813312629</v>
+        <v>0.58608458942208</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-15.42319119194109</v>
       </c>
       <c r="E86">
-        <v>-14.18864853685842</v>
+        <v>-13.64174020247806</v>
       </c>
       <c r="F86">
-        <v>-0.6071032217716335</v>
+        <v>-1.307433814638111</v>
       </c>
       <c r="G86">
-        <v>-1.075077640727877</v>
+        <v>-0.6078140011329846</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-15.28389783799461</v>
       </c>
       <c r="E87">
-        <v>-15.65554353674105</v>
+        <v>-16.35199566827671</v>
       </c>
       <c r="F87">
-        <v>-1.520324274174017</v>
+        <v>-1.602145648442238</v>
       </c>
       <c r="G87">
-        <v>-0.8718432500720188</v>
+        <v>0.1202809004100061</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-15.1444991199384</v>
       </c>
       <c r="E88">
-        <v>-17.47212277102199</v>
+        <v>-15.82930108441537</v>
       </c>
       <c r="F88">
-        <v>-1.32819699104248</v>
+        <v>-1.469166613840534</v>
       </c>
       <c r="G88">
-        <v>-0.4997710369133301</v>
+        <v>0.4449129959909388</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-15.00363263845556</v>
       </c>
       <c r="E89">
-        <v>-18.23247167080587</v>
+        <v>-18.6426880172647</v>
       </c>
       <c r="F89">
-        <v>-1.456844589965458</v>
+        <v>-1.479234232344983</v>
       </c>
       <c r="G89">
-        <v>-0.1674220596803564</v>
+        <v>0.1019206148492081</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-14.87694840048713</v>
       </c>
       <c r="E90">
-        <v>-19.85727003086197</v>
+        <v>-20.03404354222539</v>
       </c>
       <c r="F90">
-        <v>-1.479087739547805</v>
+        <v>-1.866121709692474</v>
       </c>
       <c r="G90">
-        <v>-0.2225823694556929</v>
+        <v>1.068417832311735</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-14.76648368973102</v>
       </c>
       <c r="E91">
-        <v>-22.1311028711194</v>
+        <v>-21.03105502212413</v>
       </c>
       <c r="F91">
-        <v>-1.504670924905813</v>
+        <v>-2.153876323410075</v>
       </c>
       <c r="G91">
-        <v>-0.5647106982116737</v>
+        <v>0.3051947320515376</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-14.69001995301087</v>
       </c>
       <c r="E92">
-        <v>-23.88745792957232</v>
+        <v>-23.54429016927106</v>
       </c>
       <c r="F92">
-        <v>-2.201180827251294</v>
+        <v>-2.359456396440312</v>
       </c>
       <c r="G92">
-        <v>-0.5377165098844565</v>
+        <v>0.8063484263319491</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-14.66725875488584</v>
       </c>
       <c r="E93">
-        <v>-25.96478216874091</v>
+        <v>-25.73085025845267</v>
       </c>
       <c r="F93">
-        <v>-1.742142875808212</v>
+        <v>-2.594905163035737</v>
       </c>
       <c r="G93">
-        <v>-0.03742355744425541</v>
+        <v>1.234478107107117</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-14.69664877096935</v>
       </c>
       <c r="E94">
-        <v>-27.70798201020155</v>
+        <v>-27.96370946588871</v>
       </c>
       <c r="F94">
-        <v>-2.545796818156833</v>
+        <v>-2.473604375854483</v>
       </c>
       <c r="G94">
-        <v>0.08692053301077038</v>
+        <v>0.3326192912988601</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-14.79094519985912</v>
       </c>
       <c r="E95">
-        <v>-30.26457276749792</v>
+        <v>-29.91838225079654</v>
       </c>
       <c r="F95">
-        <v>-2.427931089106167</v>
+        <v>-2.601297791963408</v>
       </c>
       <c r="G95">
-        <v>0.04842219893458574</v>
+        <v>1.161192560504271</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-14.94743859992675</v>
       </c>
       <c r="E96">
-        <v>-32.51922978456987</v>
+        <v>-31.91642649551284</v>
       </c>
       <c r="F96">
-        <v>-2.54109241973502</v>
+        <v>-2.421890834744682</v>
       </c>
       <c r="G96">
-        <v>-0.1118380000759931</v>
+        <v>0.9190890546718294</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-15.14374411414019</v>
       </c>
       <c r="E97">
-        <v>-34.42605471311266</v>
+        <v>-36.0178201195198</v>
       </c>
       <c r="F97">
-        <v>-2.889626499075356</v>
+        <v>-3.048698672339841</v>
       </c>
       <c r="G97">
-        <v>-0.9195316585652202</v>
+        <v>-0.5097225368043793</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-15.37418408106302</v>
       </c>
       <c r="E98">
-        <v>-37.62160862441731</v>
+        <v>-36.40223322108293</v>
       </c>
       <c r="F98">
-        <v>-3.097929754427192</v>
+        <v>-2.851904999728462</v>
       </c>
       <c r="G98">
-        <v>-0.6966359379516305</v>
+        <v>0.3332582265879394</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-15.61297407103699</v>
       </c>
       <c r="E99">
-        <v>-40.18971076264118</v>
+        <v>-39.65475307116706</v>
       </c>
       <c r="F99">
-        <v>-3.187792395481057</v>
+        <v>-2.975522748664003</v>
       </c>
       <c r="G99">
-        <v>-1.177469503711996</v>
+        <v>-1.323318897990127</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-15.83301159037508</v>
       </c>
       <c r="E100">
-        <v>-43.03525438941898</v>
+        <v>-42.91951112225694</v>
       </c>
       <c r="F100">
-        <v>-3.234225069215826</v>
+        <v>-3.324048909474763</v>
       </c>
       <c r="G100">
-        <v>-1.331711130932179</v>
+        <v>-0.5903475628677898</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-16.01698063144353</v>
       </c>
       <c r="E101">
-        <v>-45.01085098847926</v>
+        <v>-44.87003582497375</v>
       </c>
       <c r="F101">
-        <v>-3.709979828449328</v>
+        <v>-3.494325802090981</v>
       </c>
       <c r="G101">
-        <v>-1.647262400098891</v>
+        <v>-1.075097504001113</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-16.15109363222481</v>
       </c>
       <c r="E102">
-        <v>-46.98713138711469</v>
+        <v>-47.19565176550888</v>
       </c>
       <c r="F102">
-        <v>-3.738161875214574</v>
+        <v>-3.530874567207493</v>
       </c>
       <c r="G102">
-        <v>-2.074190352843304</v>
+        <v>-1.238959576558418</v>
       </c>
     </row>
   </sheetData>
